--- a/diseases/d200/2010-2014.xlsx
+++ b/diseases/d200/2010-2014.xlsx
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17373,7 +17373,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18663,7 +18663,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19308,7 +19308,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19714,7 +19714,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19953,7 +19953,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21004,7 +21004,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21649,7 +21649,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21888,7 +21888,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23178,7 +23178,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23584,7 +23584,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23823,7 +23823,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24229,7 +24229,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24468,7 +24468,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24874,7 +24874,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -25113,7 +25113,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25519,7 +25519,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25758,7 +25758,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26164,7 +26164,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26403,7 +26403,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26809,7 +26809,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -27048,7 +27048,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27693,7 +27693,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -28099,7 +28099,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28338,7 +28338,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28744,7 +28744,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29628,7 +29628,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -30034,7 +30034,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30273,7 +30273,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30679,7 +30679,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30918,7 +30918,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -31324,7 +31324,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31563,7 +31563,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31969,7 +31969,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32614,7 +32614,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32853,7 +32853,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -33259,7 +33259,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33498,7 +33498,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33904,7 +33904,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -34143,7 +34143,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -34549,7 +34549,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34788,7 +34788,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -35194,7 +35194,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35433,7 +35433,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -35839,7 +35839,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -36078,7 +36078,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -36484,7 +36484,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -36723,7 +36723,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -37129,7 +37129,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37368,7 +37368,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -37774,7 +37774,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -38013,7 +38013,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -38419,7 +38419,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -38658,7 +38658,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -39064,7 +39064,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -39303,7 +39303,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">

--- a/diseases/d200/2010-2014.xlsx
+++ b/diseases/d200/2010-2014.xlsx
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17373,7 +17373,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18663,7 +18663,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19308,7 +19308,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19714,7 +19714,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19953,7 +19953,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21004,7 +21004,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21649,7 +21649,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21888,7 +21888,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23178,7 +23178,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23584,7 +23584,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23823,7 +23823,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24229,7 +24229,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24468,7 +24468,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24874,7 +24874,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -25113,7 +25113,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25519,7 +25519,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25758,7 +25758,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26164,7 +26164,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26403,7 +26403,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26809,7 +26809,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -27048,7 +27048,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27693,7 +27693,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -28099,7 +28099,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28338,7 +28338,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28744,7 +28744,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29628,7 +29628,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -30034,7 +30034,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30273,7 +30273,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30679,7 +30679,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30918,7 +30918,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -31324,7 +31324,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31563,7 +31563,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31969,7 +31969,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32614,7 +32614,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32853,7 +32853,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -33259,7 +33259,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33498,7 +33498,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33904,7 +33904,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -34143,7 +34143,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -34549,7 +34549,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34788,7 +34788,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -35194,7 +35194,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35433,7 +35433,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -35839,7 +35839,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -36078,7 +36078,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -36484,7 +36484,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -36723,7 +36723,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -37129,7 +37129,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37368,7 +37368,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -37774,7 +37774,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -38013,7 +38013,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -38419,7 +38419,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -38658,7 +38658,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -39064,7 +39064,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -39303,7 +39303,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">

--- a/diseases/d200/2010-2014.xlsx
+++ b/diseases/d200/2010-2014.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>133</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.06866219678002743</v>
       </c>
@@ -1410,9 +1407,6 @@
       <c r="O5" t="n">
         <v>169</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.08724745305131305</v>
       </c>
@@ -2055,9 +2049,6 @@
       <c r="O8" t="n">
         <v>491</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.25348224525559</v>
       </c>
@@ -2700,9 +2691,6 @@
       <c r="O11" t="n">
         <v>658</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.3396971840696094</v>
       </c>
@@ -3345,9 +3333,6 @@
       <c r="O14" t="n">
         <v>1144</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.5905981437319653</v>
       </c>
@@ -3990,9 +3975,6 @@
       <c r="O17" t="n">
         <v>1337</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.6902357676308021</v>
       </c>
@@ -4635,9 +4617,6 @@
       <c r="O20" t="n">
         <v>463</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.2390270459334789</v>
       </c>
@@ -5280,9 +5259,6 @@
       <c r="O23" t="n">
         <v>988</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.510062033223061</v>
       </c>
@@ -5925,9 +5901,6 @@
       <c r="O26" t="n">
         <v>1792</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.9251327566151063</v>
       </c>
@@ -6570,9 +6543,6 @@
       <c r="O29" t="n">
         <v>2103</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>1.085688720514268</v>
       </c>
@@ -7215,9 +7185,6 @@
       <c r="O32" t="n">
         <v>2110</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>1.089302520344796</v>
       </c>
@@ -7860,9 +7827,6 @@
       <c r="O35" t="n">
         <v>996</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.5141920901722355</v>
       </c>
@@ -8505,9 +8469,6 @@
       <c r="O38" t="n">
         <v>42</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.02150705742951967</v>
       </c>
@@ -9150,9 +9111,6 @@
       <c r="O41" t="n">
         <v>63</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.0322605861442795</v>
       </c>
@@ -9795,9 +9753,6 @@
       <c r="O44" t="n">
         <v>506</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.2591088347461178</v>
       </c>
@@ -10440,9 +10395,6 @@
       <c r="O47" t="n">
         <v>429</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.2196792294586651</v>
       </c>
@@ -11085,9 +11037,6 @@
       <c r="O50" t="n">
         <v>560</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.2867607657269288</v>
       </c>
@@ -11730,9 +11679,6 @@
       <c r="O53" t="n">
         <v>898</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.459841370754968</v>
       </c>
@@ -12375,9 +12321,6 @@
       <c r="O56" t="n">
         <v>979</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.5013192672261845</v>
       </c>
@@ -13020,9 +12963,6 @@
       <c r="O59" t="n">
         <v>995</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.5095124319612396</v>
       </c>
@@ -13665,9 +13605,6 @@
       <c r="O62" t="n">
         <v>1062</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.5438213092892829</v>
       </c>
@@ -14310,9 +14247,6 @@
       <c r="O65" t="n">
         <v>1693</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.8669392435280188</v>
       </c>
@@ -14955,9 +14889,6 @@
       <c r="O68" t="n">
         <v>2371</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>1.214124599175979</v>
       </c>
@@ -15600,9 +15531,6 @@
       <c r="O71" t="n">
         <v>1530</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.7834713777896449</v>
       </c>
@@ -16245,9 +16173,6 @@
       <c r="O74" t="n">
         <v>237</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.1203802727483268</v>
       </c>
@@ -16890,9 +16815,6 @@
       <c r="O77" t="n">
         <v>295</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.1498404238850481</v>
       </c>
@@ -17535,9 +17457,6 @@
       <c r="O80" t="n">
         <v>1137</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.5775205490077957</v>
       </c>
@@ -18180,9 +18099,6 @@
       <c r="O83" t="n">
         <v>1229</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.6242504439143193</v>
       </c>
@@ -18825,9 +18741,6 @@
       <c r="O86" t="n">
         <v>2454</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>1.246469153267485</v>
       </c>
@@ -19470,9 +19383,6 @@
       <c r="O89" t="n">
         <v>1811</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.919867822562109</v>
       </c>
@@ -20115,9 +20025,6 @@
       <c r="O92" t="n">
         <v>775</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.3936485712234316</v>
       </c>
@@ -20760,9 +20667,6 @@
       <c r="O95" t="n">
         <v>1426</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.724313371051114</v>
       </c>
@@ -21405,9 +21309,6 @@
       <c r="O98" t="n">
         <v>2368</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>1.202786860202691</v>
       </c>
@@ -22050,9 +21951,6 @@
       <c r="O101" t="n">
         <v>2400</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>1.219040736691917</v>
       </c>
@@ -22695,9 +22593,6 @@
       <c r="O104" t="n">
         <v>2312</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>1.174342576346547</v>
       </c>
@@ -23340,9 +23235,6 @@
       <c r="O107" t="n">
         <v>1915</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.9726929211520922</v>
       </c>
@@ -23985,9 +23877,6 @@
       <c r="O110" t="n">
         <v>269</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.1355311893933271</v>
       </c>
@@ -24630,9 +24519,6 @@
       <c r="O113" t="n">
         <v>220</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.1108433519201932</v>
       </c>
@@ -25275,9 +25161,6 @@
       <c r="O116" t="n">
         <v>1579</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.7955529667362956</v>
       </c>
@@ -25920,9 +25803,6 @@
       <c r="O119" t="n">
         <v>1799</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.9063963186564887</v>
       </c>
@@ -26565,9 +26445,6 @@
       <c r="O122" t="n">
         <v>1437</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.724008621405989</v>
       </c>
@@ -27210,9 +27087,6 @@
       <c r="O125" t="n">
         <v>2063</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>1.03940834096072</v>
       </c>
@@ -27855,9 +27729,6 @@
       <c r="O128" t="n">
         <v>915</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.4610075773044398</v>
       </c>
@@ -28500,9 +28371,6 @@
       <c r="O131" t="n">
         <v>1471</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.741138957611837</v>
       </c>
@@ -29145,9 +29013,6 @@
       <c r="O134" t="n">
         <v>2067</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>1.041423674631997</v>
       </c>
@@ -29790,9 +29655,6 @@
       <c r="O137" t="n">
         <v>2960</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>1.491346916744417</v>
       </c>
@@ -30435,9 +30297,6 @@
       <c r="O140" t="n">
         <v>2163</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>1.089791682742627</v>
       </c>
@@ -31080,9 +30939,6 @@
       <c r="O143" t="n">
         <v>2007</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>1.011193669562853</v>
       </c>
@@ -31725,9 +31581,6 @@
       <c r="O146" t="n">
         <v>220</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.1099532000696883</v>
       </c>
@@ -32370,9 +32223,6 @@
       <c r="O149" t="n">
         <v>5894</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>2.945746187321559</v>
       </c>
@@ -33015,9 +32865,6 @@
       <c r="O152" t="n">
         <v>1209</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.6042428131102419</v>
       </c>
@@ -33660,9 +33507,6 @@
       <c r="O155" t="n">
         <v>1497</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.7481815477469247</v>
       </c>
@@ -34305,9 +34149,6 @@
       <c r="O158" t="n">
         <v>2348</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>1.173500517107401</v>
       </c>
@@ -34950,9 +34791,6 @@
       <c r="O161" t="n">
         <v>1638</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.8186515532461341</v>
       </c>
@@ -35595,9 +35433,6 @@
       <c r="O164" t="n">
         <v>1340</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.6697149458790107</v>
       </c>
@@ -36240,9 +36075,6 @@
       <c r="O167" t="n">
         <v>5902</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>2.949744485505912</v>
       </c>
@@ -36885,9 +36717,6 @@
       <c r="O170" t="n">
         <v>5235</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>2.616386374385538</v>
       </c>
@@ -37530,9 +37359,6 @@
       <c r="O173" t="n">
         <v>6039</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>3.018215341912945</v>
       </c>
@@ -38175,9 +38001,6 @@
       <c r="O176" t="n">
         <v>5857</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>2.92725405821893</v>
       </c>
@@ -38819,9 +38642,6 @@
       </c>
       <c r="O179" t="n">
         <v>1068</v>
-      </c>
-      <c r="Q179" t="n">
-        <v>0</v>
       </c>
       <c r="R179" t="n">
         <v>0.5337728076110325</v>

--- a/diseases/d200/2010-2014.xlsx
+++ b/diseases/d200/2010-2014.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17295,7 +17295,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20266,7 +20266,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20505,7 +20505,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21550,7 +21550,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22192,7 +22192,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23073,7 +23073,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23476,7 +23476,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24760,7 +24760,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24999,7 +24999,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25402,7 +25402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26044,7 +26044,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26283,7 +26283,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26686,7 +26686,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26925,7 +26925,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27567,7 +27567,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27970,7 +27970,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28209,7 +28209,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28851,7 +28851,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29254,7 +29254,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29493,7 +29493,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29896,7 +29896,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30777,7 +30777,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -31180,7 +31180,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31822,7 +31822,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -32061,7 +32061,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32464,7 +32464,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32703,7 +32703,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -33106,7 +33106,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33345,7 +33345,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33748,7 +33748,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33987,7 +33987,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -34390,7 +34390,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34629,7 +34629,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -35032,7 +35032,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -35674,7 +35674,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -35913,7 +35913,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -36316,7 +36316,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -36555,7 +36555,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -36958,7 +36958,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37197,7 +37197,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -37600,7 +37600,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -38242,7 +38242,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -38481,7 +38481,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -38884,7 +38884,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -39123,7 +39123,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">

--- a/diseases/d200/2010-2014.xlsx
+++ b/diseases/d200/2010-2014.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17295,7 +17295,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20266,7 +20266,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20505,7 +20505,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21550,7 +21550,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22192,7 +22192,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23073,7 +23073,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23476,7 +23476,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24760,7 +24760,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24999,7 +24999,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25402,7 +25402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26044,7 +26044,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26283,7 +26283,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26686,7 +26686,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26925,7 +26925,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27567,7 +27567,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27970,7 +27970,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28209,7 +28209,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28851,7 +28851,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29254,7 +29254,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29493,7 +29493,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29896,7 +29896,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30777,7 +30777,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -31180,7 +31180,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31822,7 +31822,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -32061,7 +32061,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32464,7 +32464,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32703,7 +32703,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -33106,7 +33106,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33345,7 +33345,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33748,7 +33748,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33987,7 +33987,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -34390,7 +34390,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34629,7 +34629,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -35032,7 +35032,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -35674,7 +35674,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -35913,7 +35913,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -36316,7 +36316,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -36555,7 +36555,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -36958,7 +36958,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37197,7 +37197,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -37600,7 +37600,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -38242,7 +38242,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -38481,7 +38481,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -38884,7 +38884,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -39123,7 +39123,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">

--- a/diseases/d200/2010-2014.xlsx
+++ b/diseases/d200/2010-2014.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17295,7 +17295,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20266,7 +20266,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20505,7 +20505,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21550,7 +21550,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22192,7 +22192,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23073,7 +23073,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23476,7 +23476,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24760,7 +24760,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24999,7 +24999,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25402,7 +25402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26044,7 +26044,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26283,7 +26283,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26686,7 +26686,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26925,7 +26925,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27567,7 +27567,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27970,7 +27970,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28209,7 +28209,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28851,7 +28851,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29254,7 +29254,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29493,7 +29493,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29896,7 +29896,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30777,7 +30777,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -31180,7 +31180,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31822,7 +31822,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -32061,7 +32061,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32464,7 +32464,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32703,7 +32703,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -33106,7 +33106,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33345,7 +33345,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33748,7 +33748,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33987,7 +33987,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -34390,7 +34390,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34629,7 +34629,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -35032,7 +35032,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -35674,7 +35674,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -35913,7 +35913,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -36316,7 +36316,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -36555,7 +36555,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -36958,7 +36958,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37197,7 +37197,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -37600,7 +37600,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -38242,7 +38242,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -38481,7 +38481,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -38884,7 +38884,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -39123,7 +39123,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">

--- a/diseases/d200/2010-2014.xlsx
+++ b/diseases/d200/2010-2014.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17295,7 +17295,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20266,7 +20266,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20505,7 +20505,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21550,7 +21550,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22192,7 +22192,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23073,7 +23073,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23476,7 +23476,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24760,7 +24760,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24999,7 +24999,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25402,7 +25402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26044,7 +26044,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26283,7 +26283,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26686,7 +26686,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26925,7 +26925,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27567,7 +27567,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27970,7 +27970,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28209,7 +28209,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28851,7 +28851,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29254,7 +29254,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29493,7 +29493,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29896,7 +29896,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30777,7 +30777,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -31180,7 +31180,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31822,7 +31822,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -32061,7 +32061,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32464,7 +32464,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32703,7 +32703,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -33106,7 +33106,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33345,7 +33345,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33748,7 +33748,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33987,7 +33987,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -34390,7 +34390,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34629,7 +34629,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -35032,7 +35032,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -35674,7 +35674,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -35913,7 +35913,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -36316,7 +36316,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -36555,7 +36555,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -36958,7 +36958,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37197,7 +37197,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -37600,7 +37600,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -38242,7 +38242,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -38481,7 +38481,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -38884,7 +38884,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -39123,7 +39123,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
